--- a/morpg/morpg/Assets/TableData/Table_MessageBox.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_MessageBox.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\260226morpg\morpg\morpg\Assets\Resources\TableData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\260226morpg\morpg\morpg\Assets\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,57 +19,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+  <x:si>
+    <x:t>NotSavedata</x:t>
+  </x:si>
+  <x:si>
+    <x:t>확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsEscable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GameExit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ButtonCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KoreanDesc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
+    <x:t>취소</x:t>
+  </x:si>
+  <x:si>
     <x:t>종료</x:t>
   </x:si>
   <x:si>
-    <x:t>취소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
+    <x:t>KoreanCancelButton</x:t>
   </x:si>
   <x:si>
     <x:t>KoreanConfirmButton</x:t>
   </x:si>
   <x:si>
-    <x:t>KoreanCancelButton</x:t>
-  </x:si>
-  <x:si>
     <x:t>게임을 종료하시겠습니까?</x:t>
   </x:si>
   <x:si>
-    <x:t>IsEscable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ButtonCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GameExit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KoreanDesc</x:t>
+    <x:t>세이브데이터가 없습니다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -141,7 +150,7 @@
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
@@ -150,7 +159,7 @@
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0" iLevel="0"/>
-    <x:cellStyle name="표준" xfId="1" builtinId="0"/>
+    <x:cellStyle name="표준" xfId="1"/>
   </x:cellStyles>
   <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -810,58 +819,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:G5"/>
+  <x:dimension ref="A1:G6"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="8.796875" bestFit="1" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="E2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -872,7 +885,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -886,26 +899,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>5</x:v>
+      <x:c r="D6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>